--- a/LubanConfig/Moba/Production/Datas/M-模型表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/M-模型表.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -744,6 +744,27 @@
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号占位模型</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>character/character8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LubanConfig/Moba/Production/Datas/M-模型表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/M-模型表.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -765,6 +765,69 @@
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Melee Minion</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>character/character8</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Minion</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>character/character8</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>100801</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>????-??????????</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>moba/airship/luban_airship</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
